--- a/astro-site/public/dl/guia-churreria-chocolateria/produccion-hora-punta-y-local.xlsx
+++ b/astro-site/public/dl/guia-churreria-chocolateria/produccion-hora-punta-y-local.xlsx
@@ -4108,8 +4108,8 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <mergeCells count="3">
+    <mergeCell ref="E21:H21"/>
     <mergeCell ref="E20:J20"/>
-    <mergeCell ref="E21:H21"/>
     <mergeCell ref="B29:J29"/>
   </mergeCells>
   <conditionalFormatting sqref="I6:I13">
